--- a/agriculture 24.xlsx
+++ b/agriculture 24.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -144,7 +147,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -173,6 +176,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,7 +257,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -270,8 +278,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1325,28 +1333,48 @@
         <v>-1.87101910828026</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A24:N24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:O25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 24.xlsx
+++ b/agriculture 24.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -147,7 +147,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -176,11 +176,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -257,7 +252,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -279,7 +274,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/agriculture 24.xlsx
+++ b/agriculture 24.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -274,7 +274,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
